--- a/XLibur.Tests/Resource/Other/Charts/PreserveCharts/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/Charts/PreserveCharts/outputfile.xlsx
@@ -1275,10 +1275,10 @@
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:sheetData>
     <x:row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1286,7 +1286,7 @@
       <x:c r="A2" s="1">
         <x:v>43115</x:v>
       </x:c>
-      <x:c r="B2" s="0">
+      <x:c r="B2">
         <x:f>RANDBETWEEN(1,10)</x:f>
       </x:c>
     </x:row>
@@ -1294,7 +1294,7 @@
       <x:c r="A3" s="1">
         <x:v>43146</x:v>
       </x:c>
-      <x:c r="B3" s="0">
+      <x:c r="B3">
         <x:f>RANDBETWEEN(1,10)</x:f>
       </x:c>
     </x:row>
@@ -1302,7 +1302,7 @@
       <x:c r="A4" s="1">
         <x:v>43174</x:v>
       </x:c>
-      <x:c r="B4" s="0">
+      <x:c r="B4">
         <x:f>RANDBETWEEN(1,10)</x:f>
       </x:c>
     </x:row>
@@ -1310,7 +1310,7 @@
       <x:c r="A5" s="1">
         <x:v>43205</x:v>
       </x:c>
-      <x:c r="B5" s="0">
+      <x:c r="B5">
         <x:f>RANDBETWEEN(1,10)</x:f>
       </x:c>
     </x:row>
@@ -1318,7 +1318,7 @@
       <x:c r="A6" s="1">
         <x:v>43235</x:v>
       </x:c>
-      <x:c r="B6" s="0">
+      <x:c r="B6">
         <x:f>RANDBETWEEN(1,10)</x:f>
       </x:c>
     </x:row>
@@ -1326,7 +1326,7 @@
       <x:c r="A7" s="1">
         <x:v>43266</x:v>
       </x:c>
-      <x:c r="B7" s="0">
+      <x:c r="B7">
         <x:f>RANDBETWEEN(1,10)</x:f>
       </x:c>
     </x:row>
@@ -1334,7 +1334,7 @@
       <x:c r="A8" s="1">
         <x:v>43296</x:v>
       </x:c>
-      <x:c r="B8" s="0">
+      <x:c r="B8">
         <x:f>RANDBETWEEN(1,10)</x:f>
       </x:c>
     </x:row>
